--- a/Template User Story schedule .xlsx
+++ b/Template User Story schedule .xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\road_map\PM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F209EA-FAFF-4314-AF5D-AB078BF00F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03942090-9298-4EAB-862E-CB9E09EA96D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="main" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="835" uniqueCount="495">
   <si>
     <t>#story</t>
   </si>
@@ -1640,9 +1640,6 @@
   </si>
   <si>
     <t>27 Sep 2026</t>
-  </si>
-  <si>
-    <t>4 Oct 2026</t>
   </si>
   <si>
     <t>11 Oct 2026</t>
@@ -2807,10 +2804,10 @@
         <v>479</v>
       </c>
       <c r="M5" s="95">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="97" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.3">
@@ -2848,7 +2845,7 @@
         <v>2</v>
       </c>
       <c r="N6" s="97" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="81" customHeight="1" x14ac:dyDescent="0.3">
@@ -2886,7 +2883,7 @@
         <v>3</v>
       </c>
       <c r="N7" s="97" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="83.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -2924,7 +2921,7 @@
         <v>3</v>
       </c>
       <c r="N8" s="97" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="69.599999999999994" customHeight="1" x14ac:dyDescent="0.3">
@@ -2962,7 +2959,7 @@
         <v>4</v>
       </c>
       <c r="N9" s="97" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="58.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -2998,7 +2995,7 @@
         <v>4</v>
       </c>
       <c r="N10" s="97" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3014,12 +3011,12 @@
       <c r="D11" s="97">
         <v>6</v>
       </c>
-      <c r="E11" s="95" t="s">
-        <v>52</v>
-      </c>
+      <c r="E11" s="95"/>
       <c r="F11" s="95"/>
       <c r="G11" s="95"/>
-      <c r="H11" s="95"/>
+      <c r="H11" s="95" t="s">
+        <v>52</v>
+      </c>
       <c r="I11" s="97" t="s">
         <v>95</v>
       </c>
@@ -3036,7 +3033,7 @@
         <v>5</v>
       </c>
       <c r="N11" s="97" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="67.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -3074,7 +3071,7 @@
         <v>5</v>
       </c>
       <c r="N12" s="97" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="98" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -3112,7 +3109,7 @@
         <v>6</v>
       </c>
       <c r="N13" s="97" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="98" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -3148,7 +3145,7 @@
         <v>6</v>
       </c>
       <c r="N14" s="97" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="98" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -3184,7 +3181,7 @@
         <v>7</v>
       </c>
       <c r="N15" s="97" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="98" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -3220,7 +3217,7 @@
         <v>7</v>
       </c>
       <c r="N16" s="97" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/Template User Story schedule .xlsx
+++ b/Template User Story schedule .xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\Desktop\road_map\PM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2834692-0B34-45F0-B06F-58CD751AF27D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7961E071-8C32-45EA-BF13-132F788FD7D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="901">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="900">
   <si>
     <t>#story</t>
   </si>
@@ -283,9 +283,6 @@
   </si>
   <si>
     <t>US9QATest</t>
-  </si>
-  <si>
-    <t>25 Oct 2026</t>
   </si>
   <si>
     <t>UNT Eligibility Matcher</t>
@@ -2812,7 +2809,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="39" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3062,6 +3059,11 @@
       <sz val="11"/>
       <color rgb="FF0563C1"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -3486,16 +3488,16 @@
     </xf>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4129,7 +4131,7 @@
         <v>3</v>
       </c>
       <c r="N11" s="95" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="57.6" x14ac:dyDescent="0.3">
@@ -4137,10 +4139,10 @@
         <v>18</v>
       </c>
       <c r="B12" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12" s="95" t="s">
         <v>61</v>
-      </c>
-      <c r="C12" s="95" t="s">
-        <v>62</v>
       </c>
       <c r="D12" s="95">
         <v>5</v>
@@ -4157,10 +4159,10 @@
         <v>17</v>
       </c>
       <c r="J12" s="95" t="s">
+        <v>62</v>
+      </c>
+      <c r="K12" s="102" t="s">
         <v>63</v>
-      </c>
-      <c r="K12" s="102" t="s">
-        <v>64</v>
       </c>
       <c r="L12" s="100" t="s">
         <v>36</v>
@@ -4169,7 +4171,7 @@
         <v>3</v>
       </c>
       <c r="N12" s="95" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:26" s="96" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -4177,10 +4179,10 @@
         <v>19</v>
       </c>
       <c r="B13" s="102" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="95" t="s">
         <v>65</v>
-      </c>
-      <c r="C13" s="95" t="s">
-        <v>66</v>
       </c>
       <c r="D13" s="95">
         <v>5</v>
@@ -4197,10 +4199,10 @@
         <v>17</v>
       </c>
       <c r="J13" s="95" t="s">
+        <v>66</v>
+      </c>
+      <c r="K13" s="102" t="s">
         <v>67</v>
-      </c>
-      <c r="K13" s="102" t="s">
-        <v>68</v>
       </c>
       <c r="L13" s="100" t="s">
         <v>50</v>
@@ -4209,7 +4211,7 @@
         <v>3</v>
       </c>
       <c r="N13" s="95" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:26" s="96" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -4217,10 +4219,10 @@
         <v>8</v>
       </c>
       <c r="B14" s="102" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" s="95" t="s">
         <v>69</v>
-      </c>
-      <c r="C14" s="95" t="s">
-        <v>70</v>
       </c>
       <c r="D14" s="95">
         <v>4</v>
@@ -4235,10 +4237,10 @@
         <v>17</v>
       </c>
       <c r="J14" s="95" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="102" t="s">
         <v>71</v>
-      </c>
-      <c r="K14" s="102" t="s">
-        <v>72</v>
       </c>
       <c r="L14" s="100" t="s">
         <v>36</v>
@@ -4247,7 +4249,7 @@
         <v>4</v>
       </c>
       <c r="N14" s="95" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="15" spans="1:26" s="96" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -4255,10 +4257,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="102" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="95" t="s">
         <v>74</v>
-      </c>
-      <c r="C15" s="95" t="s">
-        <v>75</v>
       </c>
       <c r="D15" s="95"/>
       <c r="E15" s="95" t="s">
@@ -4270,13 +4272,13 @@
       <c r="G15" s="95"/>
       <c r="H15" s="95"/>
       <c r="I15" s="95" t="s">
+        <v>75</v>
+      </c>
+      <c r="J15" s="95" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="95" t="s">
+      <c r="K15" s="102" t="s">
         <v>77</v>
-      </c>
-      <c r="K15" s="102" t="s">
-        <v>78</v>
       </c>
       <c r="L15" s="100" t="s">
         <v>20</v>
@@ -4285,7 +4287,7 @@
         <v>4</v>
       </c>
       <c r="N15" s="95" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
     </row>
     <row r="16" spans="1:26" s="96" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
@@ -4293,10 +4295,10 @@
         <v>20</v>
       </c>
       <c r="B16" s="102" t="s">
+        <v>79</v>
+      </c>
+      <c r="C16" s="95" t="s">
         <v>80</v>
-      </c>
-      <c r="C16" s="95" t="s">
-        <v>81</v>
       </c>
       <c r="D16" s="95">
         <v>4</v>
@@ -4311,10 +4313,10 @@
         <v>17</v>
       </c>
       <c r="J16" s="95" t="s">
+        <v>81</v>
+      </c>
+      <c r="K16" s="102" t="s">
         <v>82</v>
-      </c>
-      <c r="K16" s="102" t="s">
-        <v>83</v>
       </c>
       <c r="L16" s="100" t="s">
         <v>26</v>
@@ -4323,7 +4325,7 @@
         <v>4</v>
       </c>
       <c r="N16" s="95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4331,10 +4333,10 @@
         <v>21</v>
       </c>
       <c r="B17" s="103" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="95" t="s">
         <v>84</v>
-      </c>
-      <c r="C17" s="95" t="s">
-        <v>85</v>
       </c>
       <c r="D17" s="95">
         <v>5</v>
@@ -4349,10 +4351,10 @@
         <v>17</v>
       </c>
       <c r="J17" s="95" t="s">
+        <v>85</v>
+      </c>
+      <c r="K17" s="103" t="s">
         <v>86</v>
-      </c>
-      <c r="K17" s="103" t="s">
-        <v>87</v>
       </c>
       <c r="L17" s="100" t="s">
         <v>50</v>
@@ -4361,7 +4363,7 @@
         <v>4</v>
       </c>
       <c r="N17" s="95" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -4369,10 +4371,10 @@
         <v>6</v>
       </c>
       <c r="B18" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="95" t="s">
         <v>88</v>
-      </c>
-      <c r="C18" s="95" t="s">
-        <v>89</v>
       </c>
       <c r="D18" s="95">
         <v>6</v>
@@ -4389,10 +4391,10 @@
         <v>17</v>
       </c>
       <c r="J18" s="95" t="s">
+        <v>89</v>
+      </c>
+      <c r="K18" s="103" t="s">
         <v>90</v>
-      </c>
-      <c r="K18" s="103" t="s">
-        <v>91</v>
       </c>
       <c r="L18" s="100" t="s">
         <v>26</v>
@@ -4401,7 +4403,7 @@
         <v>5</v>
       </c>
       <c r="N18" s="95" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -4409,10 +4411,10 @@
         <v>10</v>
       </c>
       <c r="B19" s="103" t="s">
+        <v>92</v>
+      </c>
+      <c r="C19" s="95" t="s">
         <v>93</v>
-      </c>
-      <c r="C19" s="95" t="s">
-        <v>94</v>
       </c>
       <c r="D19" s="95">
         <v>6</v>
@@ -4426,13 +4428,13 @@
       <c r="G19" s="95"/>
       <c r="H19" s="95"/>
       <c r="I19" s="95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J19" s="95" t="s">
+        <v>94</v>
+      </c>
+      <c r="K19" s="103" t="s">
         <v>95</v>
-      </c>
-      <c r="K19" s="103" t="s">
-        <v>96</v>
       </c>
       <c r="L19" s="100" t="s">
         <v>36</v>
@@ -4441,7 +4443,7 @@
         <v>5</v>
       </c>
       <c r="N19" s="95" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4449,10 +4451,10 @@
         <v>22</v>
       </c>
       <c r="B20" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="C20" s="95" t="s">
         <v>98</v>
-      </c>
-      <c r="C20" s="95" t="s">
-        <v>99</v>
       </c>
       <c r="D20" s="95">
         <v>6</v>
@@ -4469,10 +4471,10 @@
         <v>17</v>
       </c>
       <c r="J20" s="95" t="s">
+        <v>99</v>
+      </c>
+      <c r="K20" s="103" t="s">
         <v>100</v>
-      </c>
-      <c r="K20" s="103" t="s">
-        <v>101</v>
       </c>
       <c r="L20" s="100" t="s">
         <v>20</v>
@@ -4481,7 +4483,7 @@
         <v>5</v>
       </c>
       <c r="N20" s="95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4489,10 +4491,10 @@
         <v>23</v>
       </c>
       <c r="B21" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="95" t="s">
         <v>102</v>
-      </c>
-      <c r="C21" s="95" t="s">
-        <v>103</v>
       </c>
       <c r="D21" s="95">
         <v>6</v>
@@ -4506,13 +4508,13 @@
       <c r="G21" s="95"/>
       <c r="H21" s="95"/>
       <c r="I21" s="95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J21" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="K21" s="103" t="s">
         <v>104</v>
-      </c>
-      <c r="K21" s="103" t="s">
-        <v>105</v>
       </c>
       <c r="L21" s="100" t="s">
         <v>50</v>
@@ -4521,7 +4523,7 @@
         <v>5</v>
       </c>
       <c r="N21" s="95" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -4529,10 +4531,10 @@
         <v>2</v>
       </c>
       <c r="B22" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="95" t="s">
         <v>106</v>
-      </c>
-      <c r="C22" s="95" t="s">
-        <v>107</v>
       </c>
       <c r="D22" s="95">
         <v>8</v>
@@ -4549,10 +4551,10 @@
         <v>17</v>
       </c>
       <c r="J22" s="95" t="s">
+        <v>107</v>
+      </c>
+      <c r="K22" s="103" t="s">
         <v>108</v>
-      </c>
-      <c r="K22" s="103" t="s">
-        <v>109</v>
       </c>
       <c r="L22" s="100" t="s">
         <v>50</v>
@@ -4561,7 +4563,7 @@
         <v>6</v>
       </c>
       <c r="N22" s="95" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4569,10 +4571,10 @@
         <v>12</v>
       </c>
       <c r="B23" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="C23" s="95" t="s">
         <v>111</v>
-      </c>
-      <c r="C23" s="95" t="s">
-        <v>112</v>
       </c>
       <c r="D23" s="95">
         <v>5</v>
@@ -4587,10 +4589,10 @@
         <v>17</v>
       </c>
       <c r="J23" s="95" t="s">
+        <v>112</v>
+      </c>
+      <c r="K23" s="103" t="s">
         <v>113</v>
-      </c>
-      <c r="K23" s="103" t="s">
-        <v>114</v>
       </c>
       <c r="L23" s="100" t="s">
         <v>50</v>
@@ -4599,7 +4601,7 @@
         <v>6</v>
       </c>
       <c r="N23" s="95" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4607,10 +4609,10 @@
         <v>24</v>
       </c>
       <c r="B24" s="103" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="95" t="s">
         <v>116</v>
-      </c>
-      <c r="C24" s="95" t="s">
-        <v>117</v>
       </c>
       <c r="D24" s="95">
         <v>5</v>
@@ -4627,10 +4629,10 @@
         <v>17</v>
       </c>
       <c r="J24" s="95" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="103" t="s">
         <v>118</v>
-      </c>
-      <c r="K24" s="103" t="s">
-        <v>119</v>
       </c>
       <c r="L24" s="100" t="s">
         <v>26</v>
@@ -4639,7 +4641,7 @@
         <v>6</v>
       </c>
       <c r="N24" s="95" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="25" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4647,10 +4649,10 @@
         <v>25</v>
       </c>
       <c r="B25" s="103" t="s">
+        <v>119</v>
+      </c>
+      <c r="C25" s="95" t="s">
         <v>120</v>
-      </c>
-      <c r="C25" s="95" t="s">
-        <v>121</v>
       </c>
       <c r="D25" s="95">
         <v>4</v>
@@ -4664,13 +4666,13 @@
       <c r="G25" s="95"/>
       <c r="H25" s="95"/>
       <c r="I25" s="95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="J25" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="K25" s="103" t="s">
         <v>122</v>
-      </c>
-      <c r="K25" s="103" t="s">
-        <v>123</v>
       </c>
       <c r="L25" s="100" t="s">
         <v>20</v>
@@ -4679,7 +4681,7 @@
         <v>6</v>
       </c>
       <c r="N25" s="95" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -4687,10 +4689,10 @@
         <v>11</v>
       </c>
       <c r="B26" s="103" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="95" t="s">
         <v>124</v>
-      </c>
-      <c r="C26" s="95" t="s">
-        <v>125</v>
       </c>
       <c r="D26" s="95">
         <v>5</v>
@@ -4707,10 +4709,10 @@
         <v>17</v>
       </c>
       <c r="J26" s="95" t="s">
+        <v>125</v>
+      </c>
+      <c r="K26" s="103" t="s">
         <v>126</v>
-      </c>
-      <c r="K26" s="103" t="s">
-        <v>127</v>
       </c>
       <c r="L26" s="100" t="s">
         <v>26</v>
@@ -4719,7 +4721,7 @@
         <v>7</v>
       </c>
       <c r="N26" s="95" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4727,10 +4729,10 @@
         <v>14</v>
       </c>
       <c r="B27" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="C27" s="95" t="s">
         <v>129</v>
-      </c>
-      <c r="C27" s="95" t="s">
-        <v>130</v>
       </c>
       <c r="D27" s="95">
         <v>4</v>
@@ -4745,10 +4747,10 @@
         <v>17</v>
       </c>
       <c r="J27" s="95" t="s">
+        <v>130</v>
+      </c>
+      <c r="K27" s="103" t="s">
         <v>131</v>
-      </c>
-      <c r="K27" s="103" t="s">
-        <v>132</v>
       </c>
       <c r="L27" s="100" t="s">
         <v>50</v>
@@ -4757,7 +4759,7 @@
         <v>7</v>
       </c>
       <c r="N27" s="95" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4765,10 +4767,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="103" t="s">
+        <v>133</v>
+      </c>
+      <c r="C28" s="95" t="s">
         <v>134</v>
-      </c>
-      <c r="C28" s="95" t="s">
-        <v>135</v>
       </c>
       <c r="D28" s="95">
         <v>7</v>
@@ -4783,10 +4785,10 @@
         <v>17</v>
       </c>
       <c r="J28" s="95" t="s">
+        <v>135</v>
+      </c>
+      <c r="K28" s="103" t="s">
         <v>136</v>
-      </c>
-      <c r="K28" s="103" t="s">
-        <v>137</v>
       </c>
       <c r="L28" s="100" t="s">
         <v>20</v>
@@ -4795,7 +4797,7 @@
         <v>7</v>
       </c>
       <c r="N28" s="95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="29" spans="1:14" ht="57.6" x14ac:dyDescent="0.3">
@@ -4803,10 +4805,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="103" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" s="95" t="s">
         <v>138</v>
-      </c>
-      <c r="C29" s="95" t="s">
-        <v>139</v>
       </c>
       <c r="D29" s="95">
         <v>3</v>
@@ -4821,10 +4823,10 @@
         <v>17</v>
       </c>
       <c r="J29" s="95" t="s">
+        <v>139</v>
+      </c>
+      <c r="K29" s="103" t="s">
         <v>140</v>
-      </c>
-      <c r="K29" s="103" t="s">
-        <v>141</v>
       </c>
       <c r="L29" s="100" t="s">
         <v>36</v>
@@ -4833,21 +4835,21 @@
         <v>7</v>
       </c>
       <c r="N29" s="95" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="8" t="s">
+        <v>142</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>143</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -4855,10 +4857,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="D32" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.3">
@@ -4866,10 +4868,10 @@
         <v>6</v>
       </c>
       <c r="C33" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="D33" s="13" t="s">
         <v>147</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>148</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -4889,10 +4891,10 @@
         <v>7</v>
       </c>
       <c r="C34" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="D34" s="14" t="s">
         <v>149</v>
-      </c>
-      <c r="D34" s="14" t="s">
-        <v>150</v>
       </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -4909,7 +4911,7 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="38" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
@@ -4947,13 +4949,13 @@
         <v>10</v>
       </c>
       <c r="L38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="M38" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="N38" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="N38" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="39" spans="1:26" ht="28.8" x14ac:dyDescent="0.3">
@@ -4961,10 +4963,10 @@
         <v>1</v>
       </c>
       <c r="B39" s="23" t="s">
+        <v>154</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>155</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>156</v>
       </c>
       <c r="D39" s="3">
         <v>3</v>
@@ -4976,22 +4978,22 @@
       <c r="G39" s="6"/>
       <c r="H39" s="7"/>
       <c r="I39" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="J39" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J39" s="3" t="s">
+      <c r="K39" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="K39" s="23" t="s">
+      <c r="L39" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="M39" s="3">
         <v>1</v>
       </c>
       <c r="N39" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>
@@ -5000,6 +5002,7 @@
       <sortCondition ref="M2:M16"/>
     </sortState>
   </autoFilter>
+  <phoneticPr fontId="38" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A3" location="'User Story1'!A1" display="'User Story1'!A1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="B3" location="'User Story1'!A1" display="Chat-Program Info" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
@@ -5102,26 +5105,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5131,28 +5134,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -5164,21 +5167,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -5190,14 +5193,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -5209,35 +5212,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -5249,28 +5252,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -5297,54 +5300,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>338</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>339</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="81" t="s">
         <v>192</v>
-      </c>
-      <c r="B4" s="81" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5353,42 +5356,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -5413,26 +5416,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5442,28 +5445,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -5475,21 +5478,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -5501,14 +5504,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -5520,35 +5523,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -5560,28 +5563,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -5608,54 +5611,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>363</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>364</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -5664,42 +5667,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -5726,26 +5729,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -5755,28 +5758,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B5" s="31"/>
       <c r="C5" s="38"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="45" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
@@ -5788,21 +5791,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="45" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -5814,14 +5817,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -5833,35 +5836,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -5873,28 +5876,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="45" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
@@ -5924,53 +5927,53 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
+        <v>386</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="104" t="s">
         <v>387</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>162</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B2" s="53" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="63" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="55" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
@@ -5979,34 +5982,34 @@
     </row>
     <row r="8" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="64" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="64" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="61" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -7021,26 +7024,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7050,28 +7053,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -7083,21 +7086,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -7109,14 +7112,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -7128,35 +7131,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -7168,28 +7171,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -7216,54 +7219,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>411</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>412</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="81" t="s">
         <v>192</v>
-      </c>
-      <c r="B4" s="81" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7272,42 +7275,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
   </sheetData>
@@ -7332,26 +7335,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -7361,28 +7364,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -7394,21 +7397,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -7420,14 +7423,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -7439,35 +7442,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -7479,28 +7482,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -7527,54 +7530,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>437</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>438</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="81" t="s">
         <v>192</v>
-      </c>
-      <c r="B4" s="81" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -7583,42 +7586,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -7646,100 +7649,100 @@
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="37"/>
       <c r="D1" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="104" t="s">
         <v>162</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="41" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="39" t="s">
         <v>164</v>
-      </c>
-      <c r="C2" s="39" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="B3" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="C3" s="40" t="s">
         <v>167</v>
-      </c>
-      <c r="C3" s="40" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="43" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C6" s="38"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="44" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="45" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="47" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A17" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A20" s="47" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A21" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.3">
@@ -7747,22 +7750,22 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A23" s="43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A25" s="47" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A26" s="45" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.3">
@@ -10710,26 +10713,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -10739,28 +10742,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -10772,21 +10775,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -10798,14 +10801,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -10817,35 +10820,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -10857,28 +10860,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -10905,54 +10908,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>463</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>464</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -10961,42 +10964,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -11021,26 +11024,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -11050,28 +11053,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -11083,21 +11086,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -11109,14 +11112,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -11128,35 +11131,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -11168,28 +11171,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -11216,54 +11219,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -11272,42 +11275,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
   </sheetData>
@@ -11332,26 +11335,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -11361,28 +11364,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -11394,21 +11397,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -11420,14 +11423,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -11439,35 +11442,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -11479,28 +11482,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -11527,54 +11530,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -11583,42 +11586,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
   </sheetData>
@@ -11643,26 +11646,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -11672,28 +11675,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -11705,21 +11708,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -11731,14 +11734,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -11750,35 +11753,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -11790,28 +11793,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -11838,54 +11841,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="97" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B2" s="98" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="84" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -11894,42 +11897,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
   </sheetData>
@@ -11954,26 +11957,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -11983,28 +11986,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -12016,21 +12019,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -12042,14 +12045,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -12061,35 +12064,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -12101,28 +12104,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -12149,54 +12152,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -12205,42 +12208,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
   </sheetData>
@@ -12268,22 +12271,22 @@
   <sheetData>
     <row r="1" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
+        <v>185</v>
+      </c>
+      <c r="D1" s="105" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="105" t="s">
         <v>186</v>
-      </c>
-      <c r="D1" s="105" t="s">
-        <v>162</v>
-      </c>
-      <c r="E1" s="105" t="s">
-        <v>187</v>
       </c>
       <c r="F1" s="9"/>
     </row>
     <row r="2" spans="1:26" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>188</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>189</v>
       </c>
       <c r="C2" s="11"/>
       <c r="D2" s="12"/>
@@ -12312,10 +12315,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
+        <v>189</v>
+      </c>
+      <c r="B3" s="54" t="s">
         <v>190</v>
-      </c>
-      <c r="B3" s="54" t="s">
-        <v>191</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="12"/>
@@ -12344,120 +12347,120 @@
     </row>
     <row r="4" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="54" t="s">
         <v>192</v>
       </c>
-      <c r="B4" s="54" t="s">
+      <c r="D4" s="106" t="s">
         <v>193</v>
-      </c>
-      <c r="D4" s="110" t="s">
-        <v>194</v>
       </c>
       <c r="E4" s="107"/>
       <c r="F4" s="9"/>
     </row>
     <row r="5" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5" s="51" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="51" t="s">
+      <c r="D5" s="12" t="s">
         <v>196</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>197</v>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="9"/>
     </row>
     <row r="6" spans="1:26" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="B6" s="56" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="56" t="s">
+      <c r="D6" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="18" t="s">
         <v>200</v>
-      </c>
-      <c r="E6" s="18" t="s">
-        <v>201</v>
       </c>
       <c r="F6" s="9"/>
     </row>
     <row r="7" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D7" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E7" s="20" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F7" s="9"/>
     </row>
     <row r="8" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
+        <v>202</v>
+      </c>
+      <c r="B8" s="59" t="s">
         <v>203</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="D8" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="E8" s="20" t="s">
         <v>204</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>205</v>
       </c>
       <c r="F8" s="9"/>
     </row>
     <row r="9" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="59" t="s">
+        <v>205</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="22" t="s">
         <v>206</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="22" t="s">
-        <v>207</v>
       </c>
       <c r="F9" s="9"/>
     </row>
     <row r="10" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="59" t="s">
+        <v>207</v>
+      </c>
+      <c r="D10" s="21" t="s">
         <v>208</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="E10" s="22" t="s">
         <v>209</v>
-      </c>
-      <c r="E10" s="22" t="s">
-        <v>210</v>
       </c>
       <c r="F10" s="9"/>
     </row>
     <row r="11" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="59" t="s">
+        <v>210</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="E11" s="22" t="s">
         <v>211</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="E11" s="22" t="s">
-        <v>212</v>
       </c>
       <c r="F11" s="9"/>
     </row>
     <row r="12" spans="1:26" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="61" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="22"/>
@@ -12465,20 +12468,20 @@
     </row>
     <row r="13" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D13" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F13" s="9"/>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C14" s="1"/>
       <c r="D14" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="1"/>
@@ -12504,108 +12507,108 @@
     </row>
     <row r="15" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D15" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F15" s="9"/>
     </row>
     <row r="16" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D16" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F16" s="9"/>
     </row>
     <row r="17" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D17" s="12" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="9"/>
     </row>
     <row r="18" spans="3:26" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D18" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F18" s="9"/>
     </row>
     <row r="19" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D19" s="19" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F19" s="9"/>
     </row>
     <row r="20" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D20" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F20" s="9"/>
     </row>
     <row r="21" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D21" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E21" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F21" s="9"/>
     </row>
     <row r="22" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D22" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E22" s="22" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="F22" s="9"/>
     </row>
     <row r="23" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D23" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E23" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F23" s="9"/>
     </row>
     <row r="24" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D24" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E24" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F24" s="9"/>
     </row>
     <row r="25" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D25" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E25" s="22" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F25" s="9"/>
     </row>
     <row r="26" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C26" s="1"/>
       <c r="D26" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E26" s="22" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F26" s="25"/>
       <c r="G26" s="1"/>
@@ -12641,71 +12644,71 @@
     </row>
     <row r="29" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D29" s="12" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="E29" s="9"/>
       <c r="F29" s="9"/>
     </row>
     <row r="30" spans="3:26" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D30" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F30" s="9"/>
     </row>
     <row r="31" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D31" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F31" s="9"/>
     </row>
     <row r="32" spans="3:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D32" s="19" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E32" s="22" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F32" s="9"/>
     </row>
     <row r="33" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D33" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E33" s="22" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F33" s="9"/>
     </row>
     <row r="34" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D34" s="21" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E34" s="22" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F34" s="9"/>
     </row>
     <row r="35" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D35" s="21" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="F35" s="9"/>
     </row>
     <row r="36" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D36" s="21" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E36" s="22" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F36" s="9"/>
     </row>
@@ -12743,73 +12746,73 @@
       <c r="Z38" s="1"/>
     </row>
     <row r="39" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="110" t="s">
-        <v>233</v>
+      <c r="D39" s="106" t="s">
+        <v>232</v>
       </c>
       <c r="E39" s="107"/>
       <c r="F39" s="9"/>
     </row>
     <row r="40" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D40" s="27" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E40" s="28"/>
       <c r="F40" s="9"/>
     </row>
     <row r="41" spans="1:26" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D41" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="E41" s="29" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F41" s="9"/>
     </row>
     <row r="42" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D42" s="30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E42" s="20"/>
       <c r="F42" s="9"/>
     </row>
     <row r="43" spans="1:26" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D43" s="108" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="E43" s="109"/>
       <c r="F43" s="9"/>
     </row>
     <row r="44" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D44" s="108" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E44" s="109"/>
       <c r="F44" s="9"/>
     </row>
     <row r="45" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D45" s="108" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E45" s="109"/>
       <c r="F45" s="9"/>
     </row>
     <row r="46" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D46" s="108" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="E46" s="109"/>
       <c r="F46" s="9"/>
     </row>
     <row r="47" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D47" s="108" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E47" s="109"/>
       <c r="F47" s="9"/>
     </row>
     <row r="48" spans="1:26" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D48" s="108" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E48" s="109"/>
       <c r="F48" s="9"/>
@@ -12819,7 +12822,7 @@
       <c r="B49" s="1"/>
       <c r="C49" s="1"/>
       <c r="D49" s="108" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E49" s="109"/>
       <c r="F49" s="25"/>
@@ -12846,7 +12849,7 @@
     </row>
     <row r="50" spans="1:26" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D50" s="108" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E50" s="109"/>
       <c r="F50" s="9"/>
@@ -12911,8 +12914,8 @@
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="C53" s="1"/>
-      <c r="D53" s="106" t="s">
-        <v>244</v>
+      <c r="D53" s="110" t="s">
+        <v>243</v>
       </c>
       <c r="E53" s="107"/>
       <c r="F53" s="25"/>
@@ -12942,7 +12945,7 @@
       <c r="B54" s="1"/>
       <c r="C54" s="1"/>
       <c r="D54" s="9" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E54" s="9"/>
       <c r="F54" s="25"/>
@@ -17791,17 +17794,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D49:E49"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="D46:E46"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D50:E50"/>
     <mergeCell ref="D48:E48"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="D45:E45"/>
     <mergeCell ref="D39:E39"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="D47:E47"/>
-    <mergeCell ref="D49:E49"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="D46:E46"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D1" location="'main'!A1" display="⬅️ Back to Main Schedule" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -17825,26 +17828,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -17854,28 +17857,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -17887,21 +17890,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -17913,14 +17916,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -17932,35 +17935,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -17972,28 +17975,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -18020,19 +18023,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B2" s="79" t="s">
         <v>39</v>
@@ -18040,34 +18043,34 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -18076,42 +18079,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
     </row>
   </sheetData>
@@ -18136,26 +18139,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -18165,28 +18168,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -18198,21 +18201,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -18224,14 +18227,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -18243,35 +18246,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -18283,28 +18286,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -18331,19 +18334,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B2" s="79" t="s">
         <v>43</v>
@@ -18351,34 +18354,34 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -18387,42 +18390,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -18447,26 +18450,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -18476,28 +18479,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -18509,21 +18512,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -18535,14 +18538,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -18554,35 +18557,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -18594,28 +18597,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -18642,19 +18645,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B2" s="79" t="s">
         <v>47</v>
@@ -18662,34 +18665,34 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -18698,42 +18701,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
   </sheetData>
@@ -18758,26 +18761,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -18787,28 +18790,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -18820,21 +18823,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -18846,14 +18849,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -18865,35 +18868,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -18905,28 +18908,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -18953,54 +18956,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -19009,42 +19012,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
   </sheetData>
@@ -19069,26 +19072,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -19098,28 +19101,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -19131,21 +19134,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -19157,14 +19160,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -19176,35 +19179,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -19216,28 +19219,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -19264,54 +19267,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -19320,42 +19323,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>
@@ -19380,26 +19383,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -19409,28 +19412,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B5" s="31"/>
       <c r="C5" s="38"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="45" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
@@ -19442,21 +19445,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="45" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -19468,14 +19471,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -19487,35 +19490,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -19527,28 +19530,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="45" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
@@ -19575,26 +19578,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -19604,28 +19607,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -19637,21 +19640,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -19663,14 +19666,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -19682,35 +19685,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -19722,28 +19725,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -19770,54 +19773,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -19826,42 +19829,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
   </sheetData>
@@ -19886,26 +19889,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -19915,28 +19918,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -19948,21 +19951,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -19974,14 +19977,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -19993,35 +19996,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -20033,28 +20036,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -20081,54 +20084,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -20137,42 +20140,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
   </sheetData>
@@ -20197,26 +20200,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -20226,28 +20229,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -20259,21 +20262,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -20285,14 +20288,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -20304,35 +20307,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -20344,28 +20347,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -20392,54 +20395,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -20448,42 +20451,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
     </row>
   </sheetData>
@@ -20508,26 +20511,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -20537,28 +20540,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -20570,21 +20573,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -20596,14 +20599,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -20615,35 +20618,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -20655,28 +20658,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -20703,54 +20706,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -20759,42 +20762,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
   </sheetData>
@@ -20819,26 +20822,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -20848,28 +20851,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -20881,21 +20884,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -20907,14 +20910,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -20926,35 +20929,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -20966,28 +20969,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -21014,54 +21017,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -21070,42 +21073,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
   </sheetData>
@@ -21130,93 +21133,93 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="104" t="s">
         <v>261</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>162</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
+        <v>262</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>263</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="54" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="61" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -21241,26 +21244,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -21270,28 +21273,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -21303,21 +21306,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -21329,14 +21332,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -21348,35 +21351,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -21388,28 +21391,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -21436,54 +21439,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -21492,42 +21495,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -21552,26 +21555,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -21581,28 +21584,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -21614,21 +21617,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -21640,14 +21643,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -21659,35 +21662,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -21699,28 +21702,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -21747,54 +21750,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -21803,42 +21806,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
   </sheetData>
@@ -21863,26 +21866,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -21892,28 +21895,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -21925,21 +21928,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -21951,14 +21954,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -21970,35 +21973,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -22010,28 +22013,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -22058,54 +22061,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B2" s="79" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B4" s="81" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -22114,42 +22117,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
   </sheetData>
@@ -22174,26 +22177,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="41" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="31"/>
       <c r="C1" s="48" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="42" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B2" s="31"/>
       <c r="C2" s="49" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -22203,28 +22206,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="43" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="31"/>
       <c r="C4" s="31"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="44" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B5" s="31"/>
       <c r="C5" s="38"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="44" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B6" s="31"/>
       <c r="C6" s="31"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="45" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B7" s="31"/>
       <c r="C7" s="31"/>
@@ -22236,21 +22239,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="43" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="31"/>
       <c r="C9" s="31"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="47" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B10" s="31"/>
       <c r="C10" s="31"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="45" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11" s="31"/>
       <c r="C11" s="31"/>
@@ -22262,14 +22265,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="43" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="31"/>
       <c r="C13" s="31"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="31"/>
       <c r="C14" s="31"/>
@@ -22281,35 +22284,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="43" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="31"/>
       <c r="C16" s="31"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="47" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B17" s="31"/>
       <c r="C17" s="31"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B18" s="31"/>
       <c r="C18" s="31"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="47" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B19" s="31"/>
       <c r="C19" s="31"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B20" s="31"/>
       <c r="C20" s="31"/>
@@ -22321,28 +22324,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="43" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="31"/>
       <c r="C22" s="31"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="47" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B23" s="31"/>
       <c r="C23" s="31"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="47" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B24" s="31"/>
       <c r="C24" s="31"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="45" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="31"/>
@@ -22369,93 +22372,93 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="52" t="s">
+        <v>285</v>
+      </c>
+      <c r="D1" s="104" t="s">
+        <v>161</v>
+      </c>
+      <c r="E1" s="104" t="s">
         <v>286</v>
-      </c>
-      <c r="D1" s="104" t="s">
-        <v>162</v>
-      </c>
-      <c r="E1" s="104" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="57" t="s">
+        <v>287</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>288</v>
-      </c>
-      <c r="B2" s="53" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="63" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="54" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="54" t="s">
         <v>192</v>
-      </c>
-      <c r="B4" s="54" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="24" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="51" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="55" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="56" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="58" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="60" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="59" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="61" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="61" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="62" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -22480,26 +22483,26 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="65" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B1" s="66"/>
       <c r="C1" s="67" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="68" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B2" s="66"/>
       <c r="C2" s="69" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -22509,28 +22512,28 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="70" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B4" s="66"/>
       <c r="C4" s="66"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="71" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B5" s="66"/>
       <c r="C5" s="72"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="71" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B6" s="66"/>
       <c r="C6" s="66"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="73" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B7" s="66"/>
       <c r="C7" s="66"/>
@@ -22542,21 +22545,21 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="70" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="66"/>
       <c r="C9" s="66"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="74" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B10" s="66"/>
       <c r="C10" s="66"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="73" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B11" s="66"/>
       <c r="C11" s="66"/>
@@ -22568,14 +22571,14 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="70" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B13" s="66"/>
       <c r="C13" s="66"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="75" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B14" s="66"/>
       <c r="C14" s="66"/>
@@ -22587,35 +22590,35 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="70" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B16" s="66"/>
       <c r="C16" s="66"/>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="74" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B17" s="66"/>
       <c r="C17" s="66"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="74" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B18" s="66"/>
       <c r="C18" s="66"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="74" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B19" s="66"/>
       <c r="C19" s="66"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="73" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B20" s="66"/>
       <c r="C20" s="66"/>
@@ -22627,28 +22630,28 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="70" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B22" s="66"/>
       <c r="C22" s="66"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="74" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B23" s="66"/>
       <c r="C23" s="66"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="74" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B24" s="66"/>
       <c r="C24" s="66"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="73" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B25" s="66"/>
       <c r="C25" s="66"/>
@@ -22675,54 +22678,54 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="77" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B1" s="66"/>
       <c r="D1" s="104" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E1" s="104" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="78" t="s">
+        <v>312</v>
+      </c>
+      <c r="B2" s="79" t="s">
         <v>313</v>
-      </c>
-      <c r="B2" s="79" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="80" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B3" s="81" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="82" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="81" t="s">
         <v>192</v>
-      </c>
-      <c r="B4" s="81" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="83" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B5" s="84" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="85" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B6" s="86" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.3">
@@ -22731,42 +22734,42 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="87" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B8" s="88" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="89" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B9" s="90" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="91" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B10" s="90" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B11" s="90" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="92" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="93" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
   </sheetData>
